--- a/RPCMixerCalculation.xlsx
+++ b/RPCMixerCalculation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="MFCmix_CO2" sheetId="1" state="visible" r:id="rId2"/>
@@ -14,6 +14,12 @@
     <sheet name="streamermix alice" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="CMS_stdLabStrada" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="2%iso_labStrada" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="0%iso_labStrada" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="CO2_30_LabStrada" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="CO2_30_iso_10_LabStrada" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="ECO65_LabStrada" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="95TFE_5iso" sheetId="12" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,6 +28,136 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ecogas:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">1ln Co2 = 1.893 Ar</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ecogas:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">1ln Co2 = 1.893 Ar</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ecogas:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">1ln Co2 = 1.893 Ar</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ecogas:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">1ln Co2 = 1.893 Ar</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -189,8 +325,113 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ecogas:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">1ln Co2 = 1.893 Ar</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ecogas:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">1ln Co2 = 1.893 Ar</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ecogas:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">1ln Co2 = 1.893 Ar</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="40">
   <si>
     <t xml:space="preserve">R134a</t>
   </si>
@@ -311,6 +552,12 @@
   <si>
     <t xml:space="preserve">Strip X</t>
   </si>
+  <si>
+    <t xml:space="preserve">Conv factor for CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ToT l/h</t>
+  </si>
 </sst>
 </file>
 
@@ -389,7 +636,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,6 +647,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD0CECE"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -533,7 +786,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -686,6 +939,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1819,6 +2080,1044 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="G1" s="38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="39" t="n">
+        <f aca="false">300/1.89</f>
+        <v>158.730158730159</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="G2" s="0" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <f aca="false">SUM(A4:D4)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <f aca="false">$A$6*A4/100</f>
+        <v>28.4</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <f aca="false">$A$6*B4/100</f>
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <f aca="false">$A$6*C4/100</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <f aca="false">($A$6*D4)/100</f>
+        <v>60.6</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <f aca="false">A8/A2*100</f>
+        <v>17.892</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <f aca="false">B8/B2*100</f>
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">C8/C2*100</f>
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">D8/D2*100</f>
+        <v>20.2</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <f aca="false">A9/$D$9*100</f>
+        <v>88.5742574257426</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <f aca="false">B9/$D$9*100</f>
+        <v>99.009900990099</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">C9/$D$9*100</f>
+        <v>49.5049504950495</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D9/$D$9*100</f>
+        <v>100</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <f aca="false">15.4/G2</f>
+        <v>8.14814814814815</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <f aca="false">SUM(A17:D17)</f>
+        <v>27.8381481481482</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <f aca="false">(E17*60)/1000</f>
+        <v>1.67028888888889</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <f aca="false">(A17/$E$17)*100</f>
+        <v>64.6594734111198</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <f aca="false">(B17/$E$17)*100</f>
+        <v>5.06499208387105</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <f aca="false">(C17/$E$17)*100</f>
+        <v>1.00581403083964</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <f aca="false">(D17/$E$17)*100</f>
+        <v>29.2697204741695</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <f aca="false">SUM(A18:D18)</f>
+        <v>100</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A13:F13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="G1" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1"/>
+      <c r="W1" s="38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="39" t="n">
+        <f aca="false">300/1.89</f>
+        <v>158.730158730159</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="Q2" s="39" t="n">
+        <f aca="false">300/1.89</f>
+        <v>158.730158730159</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <f aca="false">SUM(A4:D4)</f>
+        <v>100</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <f aca="false">SUM(Q4:T4)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+      <c r="Q6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <f aca="false">$A$6*A4/100</f>
+        <v>30</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <f aca="false">$A$6*B4/100</f>
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <f aca="false">$A$6*C4/100</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <f aca="false">($A$6*D4)/100</f>
+        <v>65</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="Q8" s="1" t="n">
+        <f aca="false">$A$6*Q4/100</f>
+        <v>30</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <f aca="false">$A$6*R4/100</f>
+        <v>4.5</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <f aca="false">$A$6*S4/100</f>
+        <v>0.5</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <f aca="false">($A$6*T4)/100</f>
+        <v>65</v>
+      </c>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <f aca="false">A8/A2*100</f>
+        <v>18.9</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <f aca="false">B8/B2*100</f>
+        <v>8</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">C8/C2*100</f>
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">D8/D2*100</f>
+        <v>21.6666666666667</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="Q9" s="6" t="n">
+        <f aca="false">Q8/Q2*100</f>
+        <v>18.9</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <f aca="false">R8/R2*100</f>
+        <v>9</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <f aca="false">S8/S2*100</f>
+        <v>5</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <f aca="false">T8/T2*100</f>
+        <v>21.6666666666667</v>
+      </c>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="1"/>
+      <c r="Q11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <f aca="false">A9/$D$9*100</f>
+        <v>87.2307692307692</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <f aca="false">B9/$D$9*100</f>
+        <v>36.9230769230769</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">C9/$D$9*100</f>
+        <v>46.1538461538462</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D9/$D$9*100</f>
+        <v>100</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="Q12" s="9" t="n">
+        <f aca="false">Q9/$D$9*100</f>
+        <v>87.2307692307692</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <f aca="false">R9/$D$9*100</f>
+        <v>41.5384615384615</v>
+      </c>
+      <c r="S12" s="11" t="n">
+        <f aca="false">S9/$D$9*100</f>
+        <v>23.0769230769231</v>
+      </c>
+      <c r="T12" s="11" t="n">
+        <f aca="false">T9/$D$9*100</f>
+        <v>100</v>
+      </c>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="Q13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="T16" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <f aca="false">30.5/1.89</f>
+        <v>16.1375661375661</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <f aca="false">SUM(A17:D17)</f>
+        <v>53.8275661375661</v>
+      </c>
+      <c r="Q17" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S17" s="27" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T17" s="0" t="n">
+        <f aca="false">30.5/1.89</f>
+        <v>16.1375661375661</v>
+      </c>
+      <c r="U17" s="13" t="n">
+        <f aca="false">SUM(Q17:T17)</f>
+        <v>53.8275661375661</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="n">
+        <f aca="false">(A17/$E$17)*100</f>
+        <v>65.0224457679382</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <f aca="false">(B17/$E$17)*100</f>
+        <v>4.49583767881173</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <f aca="false">(C17/$E$17)*100</f>
+        <v>0.501601724495523</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">(D17/$E$17)*100</f>
+        <v>29.9801148287546</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <f aca="false">SUM(A18:D18)</f>
+        <v>100</v>
+      </c>
+      <c r="Q18" s="27" t="n">
+        <f aca="false">(Q17/$E$17)*100</f>
+        <v>65.0224457679382</v>
+      </c>
+      <c r="R18" s="27" t="n">
+        <f aca="false">(R17/$E$17)*100</f>
+        <v>4.49583767881173</v>
+      </c>
+      <c r="S18" s="27" t="n">
+        <f aca="false">(S17/$E$17)*100</f>
+        <v>0.501601724495523</v>
+      </c>
+      <c r="T18" s="27" t="n">
+        <f aca="false">(T17/$E$17)*100</f>
+        <v>29.9801148287546</v>
+      </c>
+      <c r="U18" s="27" t="n">
+        <f aca="false">SUM(Q18:T18)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="Q13:V13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <f aca="false">SUM(A4:D4)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <f aca="false">$A$6*A4/100</f>
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <f aca="false">$A$6*B4/100</f>
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <f aca="false">$A$6*C4/100</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <f aca="false">($A$6*D4)/100</f>
+        <v>95</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <f aca="false">A8/A2*100</f>
+        <v>0</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <f aca="false">B8/B2*100</f>
+        <v>10</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">C8/C2*100</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">D8/D2*100</f>
+        <v>31.6666666666667</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <f aca="false">A9/$D$9*100</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <f aca="false">B9/$D$9*100</f>
+        <v>31.5789473684211</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">C9/$D$9*100</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D9/$D$9*100</f>
+        <v>100</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <f aca="false">SUM(A17:C17)</f>
+        <v>70.21</v>
+      </c>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="n">
+        <f aca="false">(A17/$D$17)*100</f>
+        <v>99.7008973080758</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <f aca="false">(B17/$D$17)*100</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <f aca="false">(C17/$D$17)*100</f>
+        <v>0.299102691924227</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">SUM(A18:C18)</f>
+        <v>100</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A13:F13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1827,6 +3126,7 @@
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.62"/>
   </cols>
@@ -1906,16 +3206,16 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>35</v>
+        <v>95.2</v>
       </c>
       <c r="E4" s="2" t="n">
         <f aca="false">SUM(A4:D4)</f>
@@ -1995,19 +3295,19 @@
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <f aca="false">($A$6*A4)/100</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B8" s="1" t="n">
         <f aca="false">$A$6*B4/100</f>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C8" s="1" t="n">
         <f aca="false">$A$6*C4/100</f>
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="D8" s="1" t="n">
         <f aca="false">($A$6*D4)/100</f>
-        <v>7</v>
+        <v>19.04</v>
       </c>
       <c r="G8" s="1" t="n">
         <f aca="false">$A$6*G4/100</f>
@@ -2030,19 +3330,19 @@
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <f aca="false">A8/A2*100</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">B8/B2*100</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">C8/C2*100</f>
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">D8/D2*100</f>
-        <v>43.75</v>
+        <v>119</v>
       </c>
       <c r="G9" s="6" t="n">
         <f aca="false">G8/G2*100</f>
@@ -2090,35 +3390,35 @@
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="n">
         <f aca="false">A9</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <f aca="false">B9/$D$9*100</f>
+        <v>75.6302521008403</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">C9/$D$9*100</f>
+        <v>25.2100840336134</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D9/$D$9*100</f>
         <v>100</v>
-      </c>
-      <c r="B12" s="10" t="n">
-        <f aca="false">B9/$A$9*100</f>
-        <v>80</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <f aca="false">C9/$A$9*100</f>
-        <v>100</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <f aca="false">D9/$A$9*100</f>
-        <v>43.75</v>
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">G9/$D$9*100</f>
-        <v>7.69523809523809</v>
+        <v>2.82913165266106</v>
       </c>
       <c r="H12" s="10" t="n">
         <f aca="false">H9/$D$9*100</f>
-        <v>6.58285714285714</v>
+        <v>2.42016806722689</v>
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">I9/$D$9*100</f>
-        <v>4.57142857142857</v>
+        <v>1.68067226890756</v>
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">J9/$D$9*100</f>
-        <v>6.29333333333333</v>
+        <v>2.31372549019608</v>
       </c>
       <c r="K12" s="1"/>
     </row>
@@ -2142,20 +3442,20 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.133</v>
+        <v>0.472</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.033</v>
+        <v>0.0315</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="E14" s="0" t="n">
         <f aca="false">SUM(A14:D14)</f>
-        <v>3.296</v>
+        <v>10.5035</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -2166,19 +3466,19 @@
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="n">
         <f aca="false">A14/$E$14</f>
-        <v>0.606796116504854</v>
+        <v>0</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">B14/$E$14</f>
-        <v>0.0403519417475728</v>
+        <v>0.0449374018184415</v>
       </c>
       <c r="C15" s="25" t="n">
         <f aca="false">C14/$E$14</f>
-        <v>0.0100121359223301</v>
+        <v>0.00299900033322226</v>
       </c>
       <c r="D15" s="25" t="n">
         <f aca="false">D14/$E$14</f>
-        <v>0.342839805825243</v>
+        <v>0.952063597848336</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -2771,7 +4071,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3033,7 +4333,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="1" style="0" width="1.96"/>
   </cols>
@@ -3802,4 +5102,825 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <f aca="false">SUM(A4:D4)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <f aca="false">$A$6*A4/100</f>
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <f aca="false">$A$6*B4/100</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <f aca="false">$A$6*C4/100</f>
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <f aca="false">($A$6*D4)/100</f>
+        <v>97.7</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <f aca="false">A8/A2*100</f>
+        <v>0</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <f aca="false">B8/B2*100</f>
+        <v>4</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">C8/C2*100</f>
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">D8/D2*100</f>
+        <v>32.5666666666667</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <f aca="false">A9/$D$9*100</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <f aca="false">B9/$D$9*100</f>
+        <v>12.2824974411464</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">C9/$D$9*100</f>
+        <v>9.21187308085977</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D9/$D$9*100</f>
+        <v>100</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <f aca="false">SUM(A17:C17)</f>
+        <v>63.03</v>
+      </c>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="n">
+        <f aca="false">(A17/$D$17)*100</f>
+        <v>95.1927653498334</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <f aca="false">(B17/$D$17)*100</f>
+        <v>4.50579089322545</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <f aca="false">(C17/$D$17)*100</f>
+        <v>0.301443756941139</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">SUM(A18:C18)</f>
+        <v>100</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A13:F13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.3"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <f aca="false">SUM(A4:D4)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <f aca="false">$A$6*A4/100</f>
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <f aca="false">$A$6*B4/100</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <f aca="false">$A$6*C4/100</f>
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <f aca="false">($A$6*D4)/100</f>
+        <v>99.7</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <f aca="false">A8/A2*100</f>
+        <v>0</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <f aca="false">B8/B2*100</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">C8/C2*100</f>
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">D8/D2*100</f>
+        <v>33.2333333333333</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <f aca="false">A9/$D$9*100</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <f aca="false">B9/$D$9*100</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">C9/$D$9*100</f>
+        <v>9.02708124373119</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D9/$D$9*100</f>
+        <v>100</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <f aca="false">SUM(A17:C17)</f>
+        <v>70.21</v>
+      </c>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="n">
+        <f aca="false">(A17/$D$17)*100</f>
+        <v>99.7008973080758</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <f aca="false">(B17/$D$17)*100</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <f aca="false">(C17/$D$17)*100</f>
+        <v>0.299102691924227</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">SUM(A18:C18)</f>
+        <v>100</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A13:F13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.56"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="G1" s="38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="39" t="n">
+        <f aca="false">300/1.89</f>
+        <v>158.730158730159</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="G2" s="0" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <f aca="false">SUM(A4:D4)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <f aca="false">$A$6*A4/100</f>
+        <v>30</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <f aca="false">$A$6*B4/100</f>
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <f aca="false">$A$6*C4/100</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <f aca="false">($A$6*D4)/100</f>
+        <v>64</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <f aca="false">A8/A2*100</f>
+        <v>18.9</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <f aca="false">B8/B2*100</f>
+        <v>10</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">C8/C2*100</f>
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">D8/D2*100</f>
+        <v>21.3333333333333</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <f aca="false">A9/$D$9*100</f>
+        <v>88.59375</v>
+      </c>
+      <c r="B12" s="10" t="n">
+        <f aca="false">B9/$D$9*100</f>
+        <v>46.875</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">C9/$D$9*100</f>
+        <v>46.875</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D9/$D$9*100</f>
+        <v>100</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <f aca="false">15.4/G2</f>
+        <v>8.14814814814815</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <f aca="false">SUM(A17:D17)</f>
+        <v>27.8381481481482</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <f aca="false">(E17*60)/1000</f>
+        <v>1.67028888888889</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <f aca="false">(A17/$E$17)*100</f>
+        <v>64.6594734111198</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <f aca="false">(B17/$E$17)*100</f>
+        <v>5.06499208387105</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <f aca="false">(C17/$E$17)*100</f>
+        <v>1.00581403083964</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <f aca="false">(D17/$E$17)*100</f>
+        <v>29.2697204741695</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <f aca="false">SUM(A18:D18)</f>
+        <v>100</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A13:F13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>